--- a/tame_output/ON/bt/strategyON_20231219.xlsx
+++ b/tame_output/ON/bt/strategyON_20231219.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-104.9%</t>
+          <t>-105.0%</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.8%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-37.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.7%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -43284,16 +43284,16 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>0.3752647008880612</v>
+        <v>0.3746595867064333</v>
       </c>
       <c r="E1816" t="n">
-        <v>3.276875380328752</v>
+        <v>3.276633334656101</v>
       </c>
       <c r="F1816" t="n">
-        <v>1.718550287702449</v>
+        <v>1.717619740283899</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.158256096908745</v>
+        <v>4.157697768457615</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231219.xlsx
+++ b/tame_output/ON/bt/strategyON_20231219.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>477.9%</t>
+          <t>478.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-37.6%</t>
         </is>
       </c>
     </row>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066012</v>
+        <v>3.074518669066013</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293021</v>
+        <v>3.087505451293022</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239774</v>
+        <v>3.125945945239775</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167861</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216942</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454038</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.09520660653793</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597766</v>
+        <v>3.147410092597767</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527685</v>
+        <v>3.120684616527686</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844645</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502547</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.14673011872803</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702054</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487811</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.14626574482338</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714842</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083875</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666732</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097097</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963478</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -43284,16 +43284,16 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>0.3746595867064333</v>
+        <v>0.3737184644086309</v>
       </c>
       <c r="E1816" t="n">
-        <v>3.276633334656101</v>
+        <v>3.276256885736979</v>
       </c>
       <c r="F1816" t="n">
-        <v>1.717619740283899</v>
+        <v>1.716654104942045</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.157697768457615</v>
+        <v>4.157118387252502</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231219.xlsx
+++ b/tame_output/ON/bt/strategyON_20231219.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>478.0%</t>
+          <t>479.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-105.0%</t>
+          <t>-110.3%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-46.8%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.6%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>105.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>-0.9%</t>
         </is>
       </c>
     </row>
@@ -43284,16 +43284,16 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>0.3737184644086309</v>
+        <v>0.3211441297159398</v>
       </c>
       <c r="E1816" t="n">
-        <v>3.276256885736979</v>
+        <v>3.255227151859903</v>
       </c>
       <c r="F1816" t="n">
-        <v>1.716654104942045</v>
+        <v>1.624582823754794</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.157118387252502</v>
+        <v>4.101875618540152</v>
       </c>
     </row>
   </sheetData>
